--- a/PTBR/Lang/PTBR/Game/Floor.xlsx
+++ b/PTBR/Lang/PTBR/Game/Floor.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Piso de Solo Sólido</t>
+          <t>piso de terra firme</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -544,12 +544,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Piso do Editor (Interior)</t>
+          <t>Piso Especial (Interno)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Editor Floor(Interior)</t>
+          <t>Special Floor (Interior)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -571,12 +571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Piso do Editor (Exterior)</t>
+          <t>Piso Especial (Externo)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Editor Floor(Exterior)</t>
+          <t>Special Floor (Exterior)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Campo</t>
+          <t>campo</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Piso de Tábua</t>
+          <t>piso de tábuas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tapete</t>
+          <t>tapete</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tapete</t>
+          <t>tapete</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tapete</t>
+          <t>tapete</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Piso de Suporte</t>
+          <t>piso de suporte</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Piso de Vidro</t>
+          <t>piso de vidro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Piso de Espelho</t>
+          <t>piso de espelho</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Piso de Metal Enferrujado</t>
+          <t>piso de metal enferrujado</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Piso de Metal</t>
+          <t>piso de metal</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Magma</t>
+          <t>magma</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Piso de Tábua</t>
+          <t>piso de troncos</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Piso de Cristal</t>
+          <t>piso de cristal</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Piso de Azulejo</t>
+          <t>piso de azulejos</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tapete</t>
+          <t>tapete</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tapete</t>
+          <t>tapete</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tapete</t>
+          <t>tapete</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Piso de Tijolos</t>
+          <t>piso de tijolos</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Piso de Areia</t>
+          <t>piso de areia</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Piso de Tábua</t>
+          <t>piso de tábuas</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Piso de Areia</t>
+          <t>piso de areia</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Piso de Grama</t>
+          <t>piso de gramado</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Piso de Grama Espessa</t>
+          <t>piso de grama alta</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Piso de Palha</t>
+          <t>piso de palha</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Piso de Solo Liso</t>
+          <t>piso de terra lisa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Piso de Gelo</t>
+          <t>piso de gelo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Piso de Neve</t>
+          <t>piso de neve</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Piso de Terra</t>
+          <t>piso de terra</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Piso de Madeira</t>
+          <t>piso de madeira</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Piso de Grama Densa</t>
+          <t>piso de grama densa</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Água</t>
+          <t>água</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Água Rasa</t>
+          <t>água rasa</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Piso de Madeira</t>
+          <t>piso de madeira</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Piso de Tábua</t>
+          <t>piso de tábuas</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Piso de Tábua</t>
+          <t>piso de tábuas</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Piso de Tijolos</t>
+          <t>piso de tijolos</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Piso de Cinzas</t>
+          <t>piso de cinzas</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Piso Moderno</t>
+          <t>piso moderno</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Piso Moderno</t>
+          <t>piso moderno</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pedestal</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Piso de Tábua</t>
+          <t>piso de tábuas</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Piso de Neve</t>
+          <t>piso de neve</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Piso de Tábua</t>
+          <t>piso de tábuas</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Piso de Tijolos</t>
+          <t>piso de tijolos</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tapete</t>
+          <t>tapete</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tapete</t>
+          <t>tapete</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tapete</t>
+          <t>tapete</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tapete</t>
+          <t>tapete</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Piso de Azulejo</t>
+          <t>piso de azulejos</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Piso de Azulejo</t>
+          <t>piso de azulejos</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Piso de Azulejo</t>
+          <t>piso de azulejos</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Piso de Azulejo</t>
+          <t>piso de azulejos</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Piso de Azulejo</t>
+          <t>piso de azulejos</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2402,22 +2402,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Alpha 11.1</t>
+          <t>EA 23.304</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Piso de Azulejo</t>
+          <t>piso fofo</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>tile floor</t>
+          <t>cute floor</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>タイルの床</t>
+          <t>かわいい床</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Águas Profundas</t>
+          <t>água profunda</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Águas Muito Rasas</t>
+          <t>água bem rasa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Piso de Areia</t>
+          <t>piso de areia</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Piso de Grama</t>
+          <t>piso de grama</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Piso de Tábua de Qualidade</t>
+          <t>piso de tábuas de qualidade</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Editor Floor(Transparente)</t>
+          <t>Piso Especial (Transparente)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Editor Floor(Transparent)</t>
+          <t>Special Floor (Transparent)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tapete Moderno</t>
+          <t>tapete moderno</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tapete Moderno</t>
+          <t>tapete moderno</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tapete Moderno</t>
+          <t>tapete moderno</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tapete Moderno</t>
+          <t>tapete moderno</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Piso com Padrão de Tábua</t>
+          <t>piso de padrão de tábuas</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Piso com Padrão de Tábua</t>
+          <t>piso de padrão de tábuas</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Piso com Padrão de Tábua</t>
+          <t>piso de padrão de tábuas</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Piso com Padrão de Tábua</t>
+          <t>piso de padrão de tábuas</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Piso com Padrão de Tábua</t>
+          <t>piso de padrão de tábuas</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Piso com Padrão de Tábua</t>
+          <t>piso de padrão de tábuas</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Piso com Padrão de Tábua</t>
+          <t>piso de padrão de tábuas</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Piso com Padrão de Tábua</t>
+          <t>piso de padrão de tábuas</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Editor Floor(Céu)</t>
+          <t>Piso Especial (Céu)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Editor Floor(Sky)</t>
+          <t>Special Floor (Sky)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Piso de Azulejo</t>
+          <t>piso de azulejos</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tapete Moderno</t>
+          <t>tapete moderno</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tatami</t>
+          <t>Tatame</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Piso de Grelha de Madeira</t>
+          <t>piso de grade de madeira</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Piso de Grelha de Madeira</t>
+          <t>piso de grade de madeira</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Piso de Grelha de Metal</t>
+          <t>piso de grade de metal</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Piso de Grelha de Metal</t>
+          <t>piso de grade de metal</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tatami</t>
+          <t>Tatame</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Piso de Caverna</t>
+          <t>piso de caverna</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Piso de Solo Estéril</t>
+          <t>piso de terra estéril</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Piso de Grama</t>
+          <t>piso de grama</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Piso de Tijolos</t>
+          <t>piso de tijolos</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Piso de Tijolos</t>
+          <t>piso de tijolos</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Pedestal</t>
+          <t>pedestal</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tapete</t>
+          <t>tapete</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Piso de Azulejo</t>
+          <t>piso de azulejos</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Piso de Azulejo</t>
+          <t>piso de azulejos</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Piso de Azulejo</t>
+          <t>piso de azulejos</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ponte</t>
+          <t>ponte</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Piso de Arbusto</t>
+          <t>piso de arbustos</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Piso de Arbusto</t>
+          <t>piso de arbustos</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Piso de Metal</t>
+          <t>piso de metal</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Piso de Metal</t>
+          <t>piso de metal</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Piso de Metal</t>
+          <t>piso de metal</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Piso de Metal</t>
+          <t>piso de metal</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Piso de Metal</t>
+          <t>piso de metal</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piso de Alga Vermelha  </t>
+          <t>piso de algas vermelhas</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piso do Fundo do Mar  </t>
+          <t>piso do leito marinho</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Piso de chocolate</t>
+          <t>piso de chocolate</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Piso de Biscoito</t>
+          <t>piso de biscoito</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Piso de Cogumelo</t>
+          <t>piso de cogumelo</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Piso de Cogumelo</t>
+          <t>piso de cogumelo</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Piso de Pedra</t>
+          <t>piso de pedra</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -3984,6 +3984,546 @@
       <c r="E132" t="inlineStr">
         <is>
           <t>石の床</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>EA 23.283</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>piso de nuvens</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>cloud floor</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>雲の床</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>EA 23.286</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>piso alienígena</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>alien floor</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>エイリアンの床</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>EA 23.288</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>piso de palco</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>stage floor</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>ステージの床</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>piso de palco</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>stage floor</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>ステージの床</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>piso alienígena</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>alien floor</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>エイリアンの床</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>piso alienígena</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>alien floor</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>エイリアンの床</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>piso alienígena</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>alien floor</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>エイリアンの床</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>EA 23.304</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>piso fofo</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>cute floor</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>かわいい床</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>EA 23.305</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>piso simples</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>plain floor</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>無地の床</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>EA 23.305</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>tapete</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>carpet</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>カーペット</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>EA 23.305</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>piso traiçoeiro</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>tricky floor</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>トリッキーな床</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>EA 23.306</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>畑</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>EA 23.306</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>piso de azulejos</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>tile floor</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>タイルの床</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>EA 23.306</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>piso de azulejos</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>tile floor</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>タイルの床</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>EA 23.307</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>piso de pedra</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>stone floor</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>石の床</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>EA 23.327</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>piso de pedra</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>stone floor</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>石の床</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>EA 23.327</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>piso de terra seca</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>dried soil floor</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>乾いた土の床</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>EA 23.327</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>piso em ruínas</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ruin floor</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>遺跡の床</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>EA 23.328</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>piso de pedra</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>stone floor</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>石の床</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>EA 23.328</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>piso de tábuas de qualidade</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>quality plank floor</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>上質板の床</t>
         </is>
       </c>
     </row>
